--- a/5/search/FY3_Missile2_results/best_solution.xlsx
+++ b/5/search/FY3_Missile2_results/best_solution.xlsx
@@ -487,37 +487,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B2" t="n">
-        <v>117.6</v>
+        <v>126</v>
       </c>
       <c r="C2" t="n">
         <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>5558.479365870453</v>
+        <v>6000</v>
       </c>
       <c r="F2" t="n">
-        <v>-212.3484275042833</v>
+        <v>24</v>
       </c>
       <c r="G2" t="n">
         <v>700</v>
       </c>
       <c r="H2" t="n">
-        <v>5484.892593515528</v>
+        <v>6000</v>
       </c>
       <c r="I2" t="n">
-        <v>252.2601679116694</v>
+        <v>276</v>
       </c>
       <c r="J2" t="n">
-        <v>621.6</v>
+        <v>680.4</v>
       </c>
       <c r="K2" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
